--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.00272709222262</v>
+        <v>10.07544315248618</v>
       </c>
       <c r="D2" t="n">
-        <v>62.43126547628074</v>
+        <v>10.14508063989562</v>
       </c>
       <c r="E2" t="n">
-        <v>11.76401385866663</v>
+        <v>1.911652252033328</v>
       </c>
       <c r="F2" t="n">
-        <v>11.14724545175973</v>
+        <v>1.811427385910956</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.42907170783854</v>
+        <v>8.357224152523763</v>
       </c>
       <c r="D3" t="n">
-        <v>51.00004796807301</v>
+        <v>8.287507794811864</v>
       </c>
       <c r="E3" t="n">
-        <v>11.76401385866663</v>
+        <v>1.911652252033328</v>
       </c>
       <c r="F3" t="n">
-        <v>11.14724545175973</v>
+        <v>1.811427385910956</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.50141129108735</v>
+        <v>5.443979334801694</v>
       </c>
       <c r="D4" t="n">
-        <v>35.24078035610588</v>
+        <v>5.726626807867206</v>
       </c>
       <c r="E4" t="n">
-        <v>11.76401385866663</v>
+        <v>1.911652252033328</v>
       </c>
       <c r="F4" t="n">
-        <v>11.14724545175973</v>
+        <v>1.811427385910956</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
